--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F234D6-D137-4C24-99D8-8379521B7732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D19A03-9E14-40AE-8DED-2681673157B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="390">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -631,10 +631,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>筛选实际收入小于8000的教授，结果放在B15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.先根据总分降序排序，再根据语文降序排序</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1410,6 +1406,10 @@
   </si>
   <si>
     <t>5. 百分比、平均值保留小数点后1位，其它数字为整数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>筛选实际收入小于8000的教授，结果放在B35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3606,13 +3606,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>2</v>
@@ -3647,7 +3647,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D2" s="16"/>
       <c r="F2" s="15">
@@ -3676,7 +3676,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D3" s="16"/>
       <c r="F3" s="15">
@@ -3705,7 +3705,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D4" s="16"/>
       <c r="F4" s="15">
@@ -3734,7 +3734,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D5" s="16"/>
       <c r="F5" s="15">
@@ -3763,7 +3763,7 @@
         <v>45</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D6" s="16"/>
       <c r="F6" s="15">
@@ -3792,7 +3792,7 @@
         <v>46</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D7" s="16"/>
       <c r="F7" s="15">
@@ -3821,7 +3821,7 @@
         <v>47</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D8" s="16"/>
       <c r="F8" s="15">
@@ -3850,7 +3850,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D9" s="16"/>
       <c r="F9" s="15">
@@ -3879,7 +3879,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D10" s="16"/>
       <c r="F10" s="15">
@@ -3908,7 +3908,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D11" s="16"/>
       <c r="F11" s="15">
@@ -3937,7 +3937,7 @@
         <v>51</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D12" s="16"/>
       <c r="F12" s="15">
@@ -3966,7 +3966,7 @@
         <v>52</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D13" s="16"/>
       <c r="F13" s="15">
@@ -3995,7 +3995,7 @@
         <v>53</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D14" s="16"/>
       <c r="F14" s="15">
@@ -4024,7 +4024,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D15" s="16"/>
       <c r="F15" s="15">
@@ -4053,7 +4053,7 @@
         <v>55</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D16" s="16"/>
       <c r="F16" s="15">
@@ -4082,7 +4082,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D17" s="16"/>
       <c r="F17" s="15">
@@ -4111,7 +4111,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D18" s="16"/>
       <c r="F18" s="15">
@@ -4137,83 +4137,83 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D20" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E20" s="19"/>
       <c r="P20" s="18"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D21" s="15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D22" s="15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E22" s="19"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D23" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D24" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E24" s="19"/>
       <c r="P24" s="18"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D25" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D26" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D27" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D28" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E28" s="19"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4246,13 +4246,13 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D1" t="s">
         <v>22</v>
@@ -4261,10 +4261,10 @@
         <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1" t="s">
         <v>24</v>
@@ -4272,13 +4272,13 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B2" s="23">
         <v>43689</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -4302,16 +4302,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B3" s="23">
         <v>43774</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -4327,21 +4327,21 @@
         <v>360</v>
       </c>
       <c r="M3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B4" s="23">
         <v>43879</v>
       </c>
       <c r="C4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -4359,16 +4359,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B5" s="23">
         <v>44004</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -4386,13 +4386,13 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6" s="23">
         <v>44084</v>
       </c>
       <c r="C6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -4413,16 +4413,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B7" s="23">
         <v>44211</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -4443,13 +4443,13 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B8" s="23">
         <v>44314</v>
       </c>
       <c r="C8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4473,13 +4473,13 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B9" s="23">
         <v>44414</v>
       </c>
       <c r="C9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -4503,13 +4503,13 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B10" s="23">
         <v>44550</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -4530,13 +4530,13 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B11" s="23">
         <v>44634</v>
       </c>
       <c r="C11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -4557,13 +4557,13 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B12" s="23">
         <v>44751</v>
       </c>
       <c r="C12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B13" s="23">
         <v>44859</v>
       </c>
       <c r="C13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -4609,18 +4609,18 @@
         <v>875</v>
       </c>
       <c r="M13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B14" s="23">
         <v>44965</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -4639,18 +4639,18 @@
         <v>825</v>
       </c>
       <c r="M14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B15" s="23">
         <v>45065</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -4669,18 +4669,18 @@
         <v>400</v>
       </c>
       <c r="M15" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="23">
         <v>45172</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -4699,18 +4699,18 @@
         <v>390</v>
       </c>
       <c r="M16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B17" s="23">
         <v>45272</v>
       </c>
       <c r="C17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -4731,16 +4731,16 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B18" s="23">
         <v>45311</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -4758,16 +4758,16 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B19" s="23">
         <v>45389</v>
       </c>
       <c r="C19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
@@ -4785,16 +4785,16 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B20" s="23">
         <v>45461</v>
       </c>
       <c r="C20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -4810,21 +4810,21 @@
         <v>650</v>
       </c>
       <c r="M20" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B21" s="23">
         <v>45529</v>
       </c>
       <c r="C21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -4840,18 +4840,18 @@
         <v>495</v>
       </c>
       <c r="M21" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B22" s="23">
         <v>45574</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -4870,18 +4870,18 @@
         <v>1920</v>
       </c>
       <c r="M22" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B23" s="23">
         <v>45627</v>
       </c>
       <c r="C23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -4900,18 +4900,18 @@
         <v>1200</v>
       </c>
       <c r="M23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B24" s="23">
         <v>45672</v>
       </c>
       <c r="C24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -4930,18 +4930,18 @@
         <v>450</v>
       </c>
       <c r="M24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B25" s="23">
         <v>45716</v>
       </c>
       <c r="C25" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -4960,18 +4960,18 @@
         <v>1920</v>
       </c>
       <c r="M25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B26" s="23">
         <v>45736</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
@@ -4990,18 +4990,18 @@
         <v>1950</v>
       </c>
       <c r="M26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B27" s="23">
         <v>45759</v>
       </c>
       <c r="C27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D27" t="s">
         <v>25</v>
@@ -5022,13 +5022,13 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B28" s="23">
         <v>45782</v>
       </c>
       <c r="C28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
@@ -5049,13 +5049,13 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B29" s="23">
         <v>45826</v>
       </c>
       <c r="C29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -5076,13 +5076,13 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B30" s="23">
         <v>45860</v>
       </c>
       <c r="C30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -5103,13 +5103,13 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B31" s="23">
         <v>45899</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D31" t="s">
         <v>20</v>
@@ -5155,23 +5155,22 @@
     <col min="13" max="13" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1"/>
     <col min="15" max="15" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="41.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9" style="1" customWidth="1"/>
+    <col min="16" max="17" width="9" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>81</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>84</v>
@@ -5183,22 +5182,22 @@
         <v>82</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I1" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J1" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="K1" s="20" t="s">
         <v>313</v>
-      </c>
-      <c r="K1" s="20" t="s">
-        <v>314</v>
       </c>
       <c r="L1" s="20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>85</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E2" s="20" t="s">
         <v>87</v>
@@ -5221,7 +5220,7 @@
         <v>86</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I2" s="20">
         <v>4700</v>
@@ -5236,7 +5235,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="20">
         <v>2</v>
       </c>
@@ -5247,10 +5246,10 @@
         <v>85</v>
       </c>
       <c r="D3" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>315</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>316</v>
       </c>
       <c r="F3" s="21">
         <v>25122</v>
@@ -5259,7 +5258,7 @@
         <v>86</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I3" s="20">
         <v>3200</v>
@@ -5274,10 +5273,10 @@
         <v>500</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="20">
         <v>3</v>
       </c>
@@ -5288,10 +5287,10 @@
         <v>85</v>
       </c>
       <c r="D4" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>315</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>316</v>
       </c>
       <c r="F4" s="21">
         <v>20950</v>
@@ -5300,7 +5299,7 @@
         <v>88</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I4" s="20">
         <v>3400</v>
@@ -5314,17 +5313,8 @@
       <c r="L4" s="20">
         <v>800</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -5335,10 +5325,10 @@
         <v>85</v>
       </c>
       <c r="D5" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>317</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>318</v>
       </c>
       <c r="F5" s="21">
         <v>22132</v>
@@ -5362,16 +5352,13 @@
         <v>1000</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="20">
         <v>5</v>
       </c>
@@ -5382,7 +5369,7 @@
         <v>90</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>87</v>
@@ -5394,7 +5381,7 @@
         <v>89</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I6" s="20">
         <v>4500</v>
@@ -5408,8 +5395,14 @@
       <c r="L6" s="20">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="20">
         <v>6</v>
       </c>
@@ -5420,7 +5413,7 @@
         <v>90</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>91</v>
@@ -5432,7 +5425,7 @@
         <v>89</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I7" s="20">
         <v>3800</v>
@@ -5447,7 +5440,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="20">
         <v>7</v>
       </c>
@@ -5458,7 +5451,7 @@
         <v>90</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>91</v>
@@ -5470,7 +5463,7 @@
         <v>86</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I8" s="20">
         <v>4300</v>
@@ -5485,7 +5478,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="20">
         <v>8</v>
       </c>
@@ -5496,10 +5489,10 @@
         <v>85</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F9" s="21">
         <v>20616</v>
@@ -5508,7 +5501,7 @@
         <v>88</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I9" s="20">
         <v>4500</v>
@@ -5523,18 +5516,18 @@
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="20">
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>91</v>
@@ -5561,7 +5554,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="20">
         <v>10</v>
       </c>
@@ -5572,7 +5565,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>91</v>
@@ -5584,7 +5577,7 @@
         <v>88</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I11" s="20">
         <v>3700</v>
@@ -5599,18 +5592,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>87</v>
@@ -5622,7 +5615,7 @@
         <v>88</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I12" s="20">
         <v>4800</v>
@@ -5637,18 +5630,18 @@
         <v>900</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>12</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>91</v>
@@ -5675,18 +5668,18 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>13</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>91</v>
@@ -5698,7 +5691,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I14" s="20">
         <v>3500</v>
@@ -5713,18 +5706,18 @@
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>14</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E15" s="20" t="s">
         <v>91</v>
@@ -5736,7 +5729,7 @@
         <v>88</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I15" s="20">
         <v>4600</v>
@@ -5751,18 +5744,18 @@
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>15</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>87</v>
@@ -5774,7 +5767,7 @@
         <v>86</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I16" s="20">
         <v>5000</v>
@@ -5794,13 +5787,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>91</v>
@@ -5812,7 +5805,7 @@
         <v>88</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I17" s="20">
         <v>3800</v>
@@ -5832,13 +5825,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>87</v>
@@ -5870,13 +5863,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>91</v>
@@ -5888,7 +5881,7 @@
         <v>89</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I19" s="20">
         <v>3400</v>
@@ -5908,13 +5901,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E20" s="20" t="s">
         <v>87</v>
@@ -5926,7 +5919,7 @@
         <v>88</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I20" s="20">
         <v>4700</v>
@@ -5946,13 +5939,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E21" s="20" t="s">
         <v>91</v>
@@ -5984,16 +5977,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F22" s="21">
         <v>35136</v>
@@ -6002,7 +5995,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I22" s="20">
         <v>2800</v>
@@ -6022,13 +6015,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>91</v>
@@ -6040,7 +6033,7 @@
         <v>88</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I23" s="20">
         <v>2800</v>
@@ -6060,16 +6053,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D24" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>317</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>318</v>
       </c>
       <c r="F24" s="21">
         <v>35800</v>
@@ -6078,7 +6071,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I24" s="20">
         <v>2600</v>
@@ -6098,13 +6091,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>91</v>
@@ -6116,7 +6109,7 @@
         <v>88</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I25" s="20">
         <v>2800</v>
@@ -6136,13 +6129,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E26" s="20" t="s">
         <v>87</v>
@@ -6154,7 +6147,7 @@
         <v>88</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I26" s="20">
         <v>2800</v>
@@ -6174,16 +6167,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D27" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>315</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>316</v>
       </c>
       <c r="F27" s="21">
         <v>36047</v>
@@ -6192,7 +6185,7 @@
         <v>89</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I27" s="20">
         <v>2600</v>
@@ -6212,16 +6205,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F28" s="21">
         <v>35273</v>
@@ -6230,7 +6223,7 @@
         <v>88</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I28" s="20">
         <v>2800</v>
@@ -6250,13 +6243,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>91</v>
@@ -6268,7 +6261,7 @@
         <v>88</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I29" s="20">
         <v>2800</v>
@@ -6288,13 +6281,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>87</v>
@@ -6306,7 +6299,7 @@
         <v>89</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I30" s="20">
         <v>2600</v>
@@ -6326,13 +6319,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>87</v>
@@ -6344,7 +6337,7 @@
         <v>88</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I31" s="20">
         <v>2800</v>
@@ -6410,7 +6403,7 @@
         <v>80</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -6434,7 +6427,7 @@
         <v>248</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -6458,7 +6451,7 @@
         <v>285</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -6792,42 +6785,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -6858,57 +6851,57 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1">
         <v>50</v>
@@ -6917,7 +6910,7 @@
         <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E2" s="5">
         <v>40945</v>
@@ -6935,30 +6928,30 @@
         <v>48</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B3" s="1">
         <v>50</v>
@@ -6967,7 +6960,7 @@
         <v>105</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E3" s="5">
         <v>40085</v>
@@ -6985,30 +6978,30 @@
         <v>680</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B4" s="1">
         <v>27</v>
@@ -7017,7 +7010,7 @@
         <v>105</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4" s="5">
         <v>42895</v>
@@ -7035,30 +7028,30 @@
         <v>260</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B5" s="1">
         <v>28</v>
@@ -7067,7 +7060,7 @@
         <v>105</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E5" s="5">
         <v>43016</v>
@@ -7085,30 +7078,30 @@
         <v>180</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6" s="1">
         <v>24</v>
@@ -7117,7 +7110,7 @@
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E6" s="5">
         <v>40146</v>
@@ -7135,31 +7128,31 @@
         <v>280</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="S6" s="2"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B7" s="1">
         <v>36</v>
@@ -7168,7 +7161,7 @@
         <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E7" s="5">
         <v>39052</v>
@@ -7186,31 +7179,31 @@
         <v>50</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="P7" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B8" s="1">
         <v>29</v>
@@ -7219,7 +7212,7 @@
         <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E8" s="5">
         <v>36677</v>
@@ -7237,31 +7230,31 @@
         <v>60</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="1">
         <v>53</v>
@@ -7270,7 +7263,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E9" s="5">
         <v>39861</v>
@@ -7288,31 +7281,31 @@
         <v>870</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S9" s="2"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B10" s="1">
         <v>32</v>
@@ -7321,7 +7314,7 @@
         <v>105</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E10" s="5">
         <v>37867</v>
@@ -7339,31 +7332,31 @@
         <v>120</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S10" s="2"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B11" s="1">
         <v>45</v>
@@ -7372,7 +7365,7 @@
         <v>108</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E11" s="5">
         <v>43561</v>
@@ -7390,31 +7383,31 @@
         <v>100</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S11" s="2"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B12" s="1">
         <v>20</v>
@@ -7423,7 +7416,7 @@
         <v>108</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E12" s="5">
         <v>37417</v>
@@ -7441,31 +7434,31 @@
         <v>120</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S12" s="2"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B13" s="1">
         <v>33</v>
@@ -7474,7 +7467,7 @@
         <v>108</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E13" s="5">
         <v>41971</v>
@@ -7492,30 +7485,30 @@
         <v>150</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B14" s="1">
         <v>23</v>
@@ -7524,7 +7517,7 @@
         <v>105</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E14" s="5">
         <v>38717</v>
@@ -7542,30 +7535,30 @@
         <v>100</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B15" s="1">
         <v>40</v>
@@ -7574,7 +7567,7 @@
         <v>105</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E15" s="5">
         <v>36811</v>
@@ -7592,30 +7585,30 @@
         <v>280</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="1">
         <v>42</v>
@@ -7624,7 +7617,7 @@
         <v>108</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E16" s="5">
         <v>43610</v>
@@ -7642,30 +7635,30 @@
         <v>200</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M16" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B17" s="1">
         <v>46</v>
@@ -7674,7 +7667,7 @@
         <v>105</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="5">
         <v>43111</v>
@@ -7692,30 +7685,30 @@
         <v>380</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M17" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="1">
         <v>27</v>
@@ -7724,7 +7717,7 @@
         <v>108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E18" s="5">
         <v>42037</v>
@@ -7742,30 +7735,30 @@
         <v>210</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L18" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" s="1">
         <v>33</v>
@@ -7774,7 +7767,7 @@
         <v>108</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E19" s="5">
         <v>42820</v>
@@ -7792,30 +7785,30 @@
         <v>48</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="O19" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="1">
         <v>18</v>
@@ -7824,7 +7817,7 @@
         <v>105</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E20" s="5">
         <v>41940</v>
@@ -7842,30 +7835,30 @@
         <v>160</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B21" s="1">
         <v>35</v>
@@ -7874,7 +7867,7 @@
         <v>108</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E21" s="5">
         <v>40444</v>
@@ -7892,30 +7885,30 @@
         <v>48</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M21" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="O21" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B22" s="1">
         <v>17</v>
@@ -7924,7 +7917,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E22" s="5">
         <v>36758</v>
@@ -7942,30 +7935,30 @@
         <v>48</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B23" s="1">
         <v>47</v>
@@ -7974,7 +7967,7 @@
         <v>108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E23" s="5">
         <v>38062</v>
@@ -7992,30 +7985,30 @@
         <v>48</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B24" s="1">
         <v>35</v>
@@ -8024,7 +8017,7 @@
         <v>105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E24" s="5">
         <v>37911</v>
@@ -8042,30 +8035,30 @@
         <v>280</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B25" s="1">
         <v>19</v>
@@ -8074,7 +8067,7 @@
         <v>108</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E25" s="5">
         <v>42927</v>
@@ -8092,30 +8085,30 @@
         <v>68</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B26" s="1">
         <v>20</v>
@@ -8124,7 +8117,7 @@
         <v>108</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E26" s="5">
         <v>41560</v>
@@ -8142,30 +8135,30 @@
         <v>100</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B27" s="1">
         <v>33</v>
@@ -8174,7 +8167,7 @@
         <v>105</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E27" s="5">
         <v>42886</v>
@@ -8192,30 +8185,30 @@
         <v>100</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B28" s="1">
         <v>23</v>
@@ -8224,7 +8217,7 @@
         <v>105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E28" s="5">
         <v>39345</v>
@@ -8242,30 +8235,30 @@
         <v>80</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B29" s="1">
         <v>57</v>
@@ -8274,7 +8267,7 @@
         <v>108</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E29" s="5">
         <v>39725</v>
@@ -8292,30 +8285,30 @@
         <v>212</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B30" s="1">
         <v>37</v>
@@ -8324,7 +8317,7 @@
         <v>105</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E30" s="5">
         <v>41797</v>
@@ -8342,30 +8335,30 @@
         <v>280</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B31" s="1">
         <v>48</v>
@@ -8374,7 +8367,7 @@
         <v>105</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E31" s="5">
         <v>42064</v>
@@ -8392,30 +8385,30 @@
         <v>420</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B32" s="1">
         <v>54</v>
@@ -8424,7 +8417,7 @@
         <v>108</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E32" s="5">
         <v>36758</v>
@@ -8442,30 +8435,30 @@
         <v>48</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L32" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B33" s="1">
         <v>50</v>
@@ -8474,7 +8467,7 @@
         <v>105</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E33" s="5">
         <v>38062</v>
@@ -8492,30 +8485,30 @@
         <v>680</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M33" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B34" s="1">
         <v>27</v>
@@ -8524,7 +8517,7 @@
         <v>105</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E34" s="5">
         <v>37911</v>
@@ -8542,30 +8535,30 @@
         <v>260</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B35" s="1">
         <v>28</v>
@@ -8574,7 +8567,7 @@
         <v>105</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E35" s="5">
         <v>42927</v>
@@ -8592,30 +8585,30 @@
         <v>180</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B36" s="1">
         <v>24</v>
@@ -8624,7 +8617,7 @@
         <v>105</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E36" s="5">
         <v>41560</v>
@@ -8642,30 +8635,30 @@
         <v>280</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B37" s="1">
         <v>36</v>
@@ -8674,7 +8667,7 @@
         <v>108</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E37" s="5">
         <v>42886</v>
@@ -8692,30 +8685,30 @@
         <v>50</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K37" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="P37" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B38" s="1">
         <v>29</v>
@@ -8724,7 +8717,7 @@
         <v>108</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E38" s="5">
         <v>39345</v>
@@ -8742,30 +8735,30 @@
         <v>60</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B39" s="1">
         <v>53</v>
@@ -8774,7 +8767,7 @@
         <v>105</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E39" s="5">
         <v>39725</v>
@@ -8792,30 +8785,30 @@
         <v>870</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B40" s="1">
         <v>32</v>
@@ -8824,7 +8817,7 @@
         <v>105</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E40" s="5">
         <v>41797</v>
@@ -8842,30 +8835,30 @@
         <v>120</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B41" s="1">
         <v>48</v>
@@ -8874,7 +8867,7 @@
         <v>108</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E41" s="5">
         <v>42064</v>
@@ -8892,30 +8885,30 @@
         <v>100</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B42" s="1">
         <v>20</v>
@@ -8924,7 +8917,7 @@
         <v>108</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E42" s="5">
         <v>36758</v>
@@ -8942,30 +8935,30 @@
         <v>120</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B43" s="1">
         <v>33</v>
@@ -8974,7 +8967,7 @@
         <v>108</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E43" s="5">
         <v>38062</v>
@@ -8992,30 +8985,30 @@
         <v>150</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B44" s="1">
         <v>23</v>
@@ -9024,7 +9017,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E44" s="5">
         <v>37911</v>
@@ -9042,30 +9035,30 @@
         <v>100</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B45" s="1">
         <v>40</v>
@@ -9074,7 +9067,7 @@
         <v>105</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E45" s="5">
         <v>42927</v>
@@ -9092,30 +9085,30 @@
         <v>280</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B46" s="1">
         <v>42</v>
@@ -9124,7 +9117,7 @@
         <v>108</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" s="5">
         <v>41560</v>
@@ -9142,30 +9135,30 @@
         <v>200</v>
       </c>
       <c r="J46" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M46" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B47" s="1">
         <v>46</v>
@@ -9174,7 +9167,7 @@
         <v>105</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E47" s="5">
         <v>42886</v>
@@ -9192,30 +9185,30 @@
         <v>380</v>
       </c>
       <c r="J47" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="M47" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B48" s="1">
         <v>27</v>
@@ -9224,7 +9217,7 @@
         <v>108</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E48" s="5">
         <v>39345</v>
@@ -9242,30 +9235,30 @@
         <v>210</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B49" s="1">
         <v>33</v>
@@ -9274,7 +9267,7 @@
         <v>108</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E49" s="5">
         <v>39725</v>
@@ -9292,30 +9285,30 @@
         <v>48</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L49" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="N49" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="O49" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B50" s="1">
         <v>18</v>
@@ -9324,7 +9317,7 @@
         <v>105</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E50" s="5">
         <v>41797</v>
@@ -9342,30 +9335,30 @@
         <v>160</v>
       </c>
       <c r="J50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B51" s="1">
         <v>35</v>
@@ -9374,7 +9367,7 @@
         <v>108</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E51" s="5">
         <v>42064</v>
@@ -9392,30 +9385,30 @@
         <v>48</v>
       </c>
       <c r="J51" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L51" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M51" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="O51" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B52" s="1">
         <v>17</v>
@@ -9424,7 +9417,7 @@
         <v>108</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E52" s="5">
         <v>36758</v>
@@ -9442,30 +9435,30 @@
         <v>48</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -9474,7 +9467,7 @@
         <v>108</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E53" s="5">
         <v>38062</v>
@@ -9492,30 +9485,30 @@
         <v>48</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B54" s="1">
         <v>35</v>
@@ -9524,7 +9517,7 @@
         <v>105</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E54" s="5">
         <v>37911</v>
@@ -9542,30 +9535,30 @@
         <v>280</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B55" s="1">
         <v>19</v>
@@ -9574,7 +9567,7 @@
         <v>108</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E55" s="5">
         <v>42927</v>
@@ -9592,30 +9585,30 @@
         <v>68</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B56" s="1">
         <v>20</v>
@@ -9624,7 +9617,7 @@
         <v>108</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E56" s="5">
         <v>41560</v>
@@ -9642,30 +9635,30 @@
         <v>100</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B57" s="1">
         <v>33</v>
@@ -9674,7 +9667,7 @@
         <v>105</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E57" s="5">
         <v>42886</v>
@@ -9692,30 +9685,30 @@
         <v>100</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B58" s="1">
         <v>23</v>
@@ -9724,7 +9717,7 @@
         <v>105</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E58" s="5">
         <v>39345</v>
@@ -9742,30 +9735,30 @@
         <v>80</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B59" s="1">
         <v>50</v>
@@ -9774,7 +9767,7 @@
         <v>108</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E59" s="5">
         <v>39725</v>
@@ -9792,30 +9785,30 @@
         <v>212</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B60" s="1">
         <v>37</v>
@@ -9824,7 +9817,7 @@
         <v>105</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E60" s="5">
         <v>41797</v>
@@ -9842,30 +9835,30 @@
         <v>280</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B61" s="1">
         <v>48</v>
@@ -9874,7 +9867,7 @@
         <v>105</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E61" s="5">
         <v>42064</v>
@@ -9892,25 +9885,25 @@
         <v>420</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -9930,13 +9923,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -9961,7 +9954,7 @@
         <v>0.3614</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q3" s="13">
         <v>12</v>
@@ -9981,13 +9974,13 @@
         <v>0.33119999999999999</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q4" s="13">
         <v>23</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -10001,10 +9994,10 @@
         <v>0.42280000000000001</v>
       </c>
       <c r="P5" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q5" s="13" t="s">
         <v>288</v>
-      </c>
-      <c r="Q5" s="13" t="s">
-        <v>289</v>
       </c>
       <c r="R5" s="13">
         <v>123</v>
